--- a/public/samples/participant_list_sample.xlsx
+++ b/public/samples/participant_list_sample.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Participants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Acme Pty Ltd</t>
+          <t>Bob Wilson</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
